--- a/data/trans_orig/P05A06-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05A06-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2012</t>
+          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2012 (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>285426</t>
+          <t>283826</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>324224</t>
+          <t>324961</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>206171</t>
+          <t>207588</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>240346</t>
+          <t>240624</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>502173</t>
+          <t>503554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>556119</t>
+          <t>558197</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,26%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92833</t>
+          <t>93603</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>129705</t>
+          <t>129962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,82 +860,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>29,73%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>84196</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>68981</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>101353</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>26,78%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>21,94%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>32,23%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>195145</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>169579</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>223046</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>25,96%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>22,56%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>29,67%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>84196</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>69188</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>102480</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>26,78%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>32,59%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>195145</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>170666</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>222250</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>25,96%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>22,71%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31821</t>
+          <t>31813</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13271</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17518</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38982</t>
+          <t>41633</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>288248</t>
+          <t>284712</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>326687</t>
+          <t>325099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>216971</t>
+          <t>216502</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>252279</t>
+          <t>252925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>515353</t>
+          <t>518109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>568393</t>
+          <t>570529</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,08%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79373</t>
+          <t>80042</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>117357</t>
+          <t>119869</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71959</t>
+          <t>72965</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>106468</t>
+          <t>107582</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>163149</t>
+          <t>160391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>213386</t>
+          <t>211541</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>15082</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21367</t>
+          <t>21716</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12176</t>
+          <t>12787</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31006</t>
+          <t>30826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>404015</t>
+          <t>402487</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>453394</t>
+          <t>452054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>174468</t>
+          <t>174728</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>204100</t>
+          <t>203534</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>589864</t>
+          <t>587260</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>647270</t>
+          <t>647360</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,41%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140749</t>
+          <t>140432</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187576</t>
+          <t>189200</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46545</t>
+          <t>46674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74752</t>
+          <t>75093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198031</t>
+          <t>197161</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>250421</t>
+          <t>251875</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21190</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>44942</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18458</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26697</t>
+          <t>28656</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53847</t>
+          <t>54597</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>777967</t>
+          <t>776776</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>841451</t>
+          <t>843933</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>482913</t>
+          <t>484145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>536221</t>
+          <t>536359</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1278537</t>
+          <t>1278241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1360248</t>
+          <t>1362689</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>261541</t>
+          <t>262305</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>326142</t>
+          <t>325868</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>190903</t>
+          <t>190278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>243488</t>
+          <t>239935</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>470144</t>
+          <t>466081</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>549228</t>
+          <t>547329</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36980</t>
+          <t>37578</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65358</t>
+          <t>68569</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23696</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48395</t>
+          <t>48973</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>67072</t>
+          <t>67183</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>106445</t>
+          <t>105031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>358372</t>
+          <t>358699</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>399691</t>
+          <t>398620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>543401</t>
+          <t>544830</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>591729</t>
+          <t>591955</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>919055</t>
+          <t>912927</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>980346</t>
+          <t>977504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,26%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>90584</t>
+          <t>89462</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>131768</t>
+          <t>129677</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>141355</t>
+          <t>144653</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>190372</t>
+          <t>189240</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>244798</t>
+          <t>246187</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>303504</t>
+          <t>308904</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12280</t>
+          <t>12088</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29493</t>
+          <t>30252</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>13859</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32320</t>
+          <t>33207</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30099</t>
+          <t>30982</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55579</t>
+          <t>55664</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>177004</t>
+          <t>179367</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>208290</t>
+          <t>206199</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>742848</t>
+          <t>741553</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>805311</t>
+          <t>804656</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>934375</t>
+          <t>934919</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1001955</t>
+          <t>1002145</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53822</t>
+          <t>57211</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85007</t>
+          <t>83594</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>264316</t>
+          <t>263181</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>325178</t>
+          <t>325950</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>329836</t>
+          <t>329379</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>394463</t>
+          <t>394613</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>9815</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24448</t>
+          <t>23918</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47520</t>
+          <t>47298</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28728</t>
+          <t>28213</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>52878</t>
+          <t>52106</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2365939</t>
+          <t>2371990</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2477329</t>
+          <t>2478956</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2443694</t>
+          <t>2445055</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2555324</t>
+          <t>2558099</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4850116</t>
+          <t>4846843</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5004719</t>
+          <t>5003892</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>793499</t>
+          <t>794817</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>898203</t>
+          <t>895730</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>855214</t>
+          <t>857941</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>970756</t>
+          <t>964596</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1680131</t>
+          <t>1677540</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1828048</t>
+          <t>1838600</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>111675</t>
+          <t>111565</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>159472</t>
+          <t>157834</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>95918</t>
+          <t>96744</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>139989</t>
+          <t>141847</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>220806</t>
+          <t>221480</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>284740</t>
+          <t>286039</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2016</t>
+          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2016 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>320099</t>
+          <t>319422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>354646</t>
+          <t>354429</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>251138</t>
+          <t>251398</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>283241</t>
+          <t>282570</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>581915</t>
+          <t>581481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>627171</t>
+          <t>630083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60232</t>
+          <t>61136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93041</t>
+          <t>94011</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51587</t>
+          <t>52546</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82273</t>
+          <t>80937</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122139</t>
+          <t>121220</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>164873</t>
+          <t>165451</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19749</t>
+          <t>19236</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33611</t>
+          <t>33902</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>266622</t>
+          <t>267071</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>300122</t>
+          <t>300655</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262228</t>
+          <t>262057</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>297087</t>
+          <t>296911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>542819</t>
+          <t>540542</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>588197</t>
+          <t>586585</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69119</t>
+          <t>67403</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>101226</t>
+          <t>100448</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60938</t>
+          <t>61725</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94032</t>
+          <t>94549</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>135892</t>
+          <t>138590</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>182433</t>
+          <t>184619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12443</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10735</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27987</t>
+          <t>27956</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>373247</t>
+          <t>373181</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>413224</t>
+          <t>413413</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>123032</t>
+          <t>123817</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>144251</t>
+          <t>143839</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>504237</t>
+          <t>504631</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>550086</t>
+          <t>549553</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86279</t>
+          <t>88023</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122457</t>
+          <t>122940</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17857</t>
+          <t>17620</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37536</t>
+          <t>37050</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111770</t>
+          <t>112241</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>154496</t>
+          <t>151778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14295</t>
+          <t>14047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34429</t>
+          <t>33157</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12196</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>18700</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39828</t>
+          <t>41465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>802758</t>
+          <t>805115</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>864787</t>
+          <t>865266</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>603273</t>
+          <t>602389</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>655101</t>
+          <t>653370</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1423370</t>
+          <t>1424410</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1497859</t>
+          <t>1504448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,48%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>232195</t>
+          <t>230257</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>291310</t>
+          <t>286525</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142188</t>
+          <t>142817</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>189982</t>
+          <t>191604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>392970</t>
+          <t>386307</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>463499</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>37891</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66395</t>
+          <t>68913</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>18013</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38184</t>
+          <t>37913</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>61894</t>
+          <t>61520</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>97344</t>
+          <t>96582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>466418</t>
+          <t>467696</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>506517</t>
+          <t>508053</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>524094</t>
+          <t>523997</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>571718</t>
+          <t>569905</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1007363</t>
+          <t>1007791</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1069452</t>
+          <t>1066745</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,2%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>92851</t>
+          <t>91844</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>130029</t>
+          <t>129192</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>130543</t>
+          <t>131691</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>175447</t>
+          <t>175908</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>234645</t>
+          <t>233864</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>291835</t>
+          <t>293213</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>26700</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21121</t>
+          <t>20320</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42008</t>
+          <t>41481</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34424</t>
+          <t>34543</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61567</t>
+          <t>60644</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>213828</t>
+          <t>215574</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>240692</t>
+          <t>243414</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>776679</t>
+          <t>773356</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>833766</t>
+          <t>833801</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1004595</t>
+          <t>1001926</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1069191</t>
+          <t>1067210</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,76%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36723</t>
+          <t>34888</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>60141</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>200684</t>
+          <t>200420</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>258185</t>
+          <t>257039</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>243194</t>
+          <t>243939</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>305756</t>
+          <t>306477</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>24744</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>52072</t>
+          <t>51918</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31706</t>
+          <t>30794</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>60051</t>
+          <t>58489</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2519796</t>
+          <t>2516162</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2618086</t>
+          <t>2614429</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2617722</t>
+          <t>2614285</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2716700</t>
+          <t>2722642</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5161708</t>
+          <t>5163471</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5300982</t>
+          <t>5302836</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>636279</t>
+          <t>636161</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>729417</t>
+          <t>731182</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>668503</t>
+          <t>665112</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>765333</t>
+          <t>764995</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1332552</t>
+          <t>1333433</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1461747</t>
+          <t>1461295</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97208</t>
+          <t>97190</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>140627</t>
+          <t>142584</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>98122</t>
+          <t>99151</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>144311</t>
+          <t>145650</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>207083</t>
+          <t>206154</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>270005</t>
+          <t>272598</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2023</t>
+          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2023 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>399845</t>
+          <t>396820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>435292</t>
+          <t>433509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>371493</t>
+          <t>371566</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>397079</t>
+          <t>398975</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>779778</t>
+          <t>780107</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>824068</t>
+          <t>825656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50152</t>
+          <t>50118</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79516</t>
+          <t>81311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,82 +7712,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16,13%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>47864</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>37563</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>62216</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>112423</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>94461</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>132718</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>11,85%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>9,95%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>47864</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>38097</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62426</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>10,76%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>112423</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>94233</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>132856</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>11,85%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>12847</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>40723</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16041</t>
+          <t>17594</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22882</t>
+          <t>21976</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50619</t>
+          <t>50622</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>373222</t>
+          <t>374736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>402841</t>
+          <t>404784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299224</t>
+          <t>299454</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>326175</t>
+          <t>325798</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>681758</t>
+          <t>683246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>722220</t>
+          <t>721589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,58%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38208</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66563</t>
+          <t>65486</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43946</t>
+          <t>44747</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68785</t>
+          <t>68644</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>88764</t>
+          <t>89624</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>124592</t>
+          <t>126439</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19560</t>
+          <t>19027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>21911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>15817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33960</t>
+          <t>34419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>539425</t>
+          <t>536686</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644433</t>
+          <t>638629</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>131921</t>
+          <t>131568</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>147539</t>
+          <t>147091</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>678556</t>
+          <t>679806</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>795843</t>
+          <t>783959</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>21276</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95392</t>
+          <t>98528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15324</t>
+          <t>15609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30479</t>
+          <t>30342</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29088</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119747</t>
+          <t>117866</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38391</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41268</t>
+          <t>41251</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>825159</t>
+          <t>826494</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>882314</t>
+          <t>883584</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>796880</t>
+          <t>797368</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>903081</t>
+          <t>915609</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1647630</t>
+          <t>1649094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1794728</t>
+          <t>1805450</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,98%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105116</t>
+          <t>105313</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160174</t>
+          <t>156793</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55992</t>
+          <t>47787</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141723</t>
+          <t>142583</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>162679</t>
+          <t>156821</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>275506</t>
+          <t>279361</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32490</t>
+          <t>32180</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62854</t>
+          <t>63479</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>13189</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41949</t>
+          <t>41846</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49464</t>
+          <t>50964</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>97401</t>
+          <t>95852</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>370664</t>
+          <t>369247</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>404040</t>
+          <t>403632</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>663400</t>
+          <t>663588</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>729178</t>
+          <t>728878</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1046771</t>
+          <t>1048167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1120182</t>
+          <t>1121290</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,43%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43903</t>
+          <t>44753</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>72820</t>
+          <t>73401</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>73793</t>
+          <t>73115</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>122669</t>
+          <t>121102</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>130016</t>
+          <t>128400</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>183972</t>
+          <t>182385</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>17455</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38160</t>
+          <t>37144</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33794</t>
+          <t>35258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64053</t>
+          <t>64674</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58417</t>
+          <t>56825</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94439</t>
+          <t>93479</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>170850</t>
+          <t>171115</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>211711</t>
+          <t>211924</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>601744</t>
+          <t>601317</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>644241</t>
+          <t>644908</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>786634</t>
+          <t>788194</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>846882</t>
+          <t>844717</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,59%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16470</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53195</t>
+          <t>47077</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86830</t>
+          <t>87115</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>125320</t>
+          <t>124616</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>111051</t>
+          <t>111229</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162003</t>
+          <t>164091</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32993</t>
+          <t>33694</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20931</t>
+          <t>21185</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45410</t>
+          <t>45670</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31432</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>67729</t>
+          <t>65311</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2772351</t>
+          <t>2780108</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2963201</t>
+          <t>2978687</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2934947</t>
+          <t>2936888</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3097567</t>
+          <t>3102764</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5736977</t>
+          <t>5731257</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5993513</t>
+          <t>5977863</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,2%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>307342</t>
+          <t>285221</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>440630</t>
+          <t>435147</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>362001</t>
+          <t>361158</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>487373</t>
+          <t>486188</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>705313</t>
+          <t>720807</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>896231</t>
+          <t>911476</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>102696</t>
+          <t>106968</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>173844</t>
+          <t>169549</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>112370</t>
+          <t>109929</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>163288</t>
+          <t>162461</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>235154</t>
+          <t>234352</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>321186</t>
+          <t>320129</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A06-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05A06-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>283826</t>
+          <t>284124</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>324961</t>
+          <t>323208</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>207588</t>
+          <t>207600</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>240624</t>
+          <t>240946</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>503554</t>
+          <t>500322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>558197</t>
+          <t>554354</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,75%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93603</t>
+          <t>92751</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>129962</t>
+          <t>131087</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68981</t>
+          <t>68711</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101353</t>
+          <t>100629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>169579</t>
+          <t>169324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>223046</t>
+          <t>220825</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12730</t>
+          <t>13562</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31813</t>
+          <t>34043</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12586</t>
+          <t>12673</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18371</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41633</t>
+          <t>39241</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>284712</t>
+          <t>288226</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>325099</t>
+          <t>326285</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>216502</t>
+          <t>216867</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>252925</t>
+          <t>253106</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>518109</t>
+          <t>517424</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>570529</t>
+          <t>569122</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,89%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80042</t>
+          <t>81207</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>119869</t>
+          <t>116990</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72965</t>
+          <t>73334</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107582</t>
+          <t>108008</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>160391</t>
+          <t>160019</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>211541</t>
+          <t>211048</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15082</t>
+          <t>15074</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>20941</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12787</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30826</t>
+          <t>30546</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>402487</t>
+          <t>401070</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>452054</t>
+          <t>449949</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>174728</t>
+          <t>173972</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>203534</t>
+          <t>203906</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>587260</t>
+          <t>588147</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>647360</t>
+          <t>643321</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>72,96%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140432</t>
+          <t>141361</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189200</t>
+          <t>188254</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46674</t>
+          <t>46177</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75093</t>
+          <t>74781</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>197161</t>
+          <t>200330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>251875</t>
+          <t>251347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21331</t>
+          <t>21135</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44942</t>
+          <t>46014</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28656</t>
+          <t>27936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54597</t>
+          <t>54863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>776776</t>
+          <t>774753</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>843933</t>
+          <t>842886</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>484145</t>
+          <t>482796</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>536359</t>
+          <t>536282</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1278241</t>
+          <t>1278023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1362689</t>
+          <t>1362042</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,17%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>262305</t>
+          <t>262412</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>325868</t>
+          <t>326640</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>190278</t>
+          <t>191005</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>239935</t>
+          <t>240745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>466081</t>
+          <t>466452</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>547329</t>
+          <t>547762</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37578</t>
+          <t>36931</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68569</t>
+          <t>68084</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24401</t>
+          <t>24305</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48973</t>
+          <t>49305</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>67183</t>
+          <t>67861</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>105031</t>
+          <t>105647</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>358699</t>
+          <t>359226</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>398620</t>
+          <t>398215</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>544830</t>
+          <t>544193</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>591955</t>
+          <t>592277</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>912927</t>
+          <t>916116</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>977504</t>
+          <t>979504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,42%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89462</t>
+          <t>90297</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>129677</t>
+          <t>127735</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>144653</t>
+          <t>142571</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>189240</t>
+          <t>190320</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>246187</t>
+          <t>244121</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>308904</t>
+          <t>305118</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30252</t>
+          <t>29646</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,77 +2797,77 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>22137</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>14535</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>33667</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>41840</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>30050</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>55642</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>2,38%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>22137</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>13859</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>33207</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>41840</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>30982</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>55664</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>179367</t>
+          <t>180030</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>206199</t>
+          <t>208012</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>741553</t>
+          <t>744863</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>804656</t>
+          <t>803971</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>934919</t>
+          <t>933342</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1002145</t>
+          <t>998390</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>72,94%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57211</t>
+          <t>54233</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>83594</t>
+          <t>82395</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>263181</t>
+          <t>264959</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>325950</t>
+          <t>321541</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>329379</t>
+          <t>330064</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>394613</t>
+          <t>395059</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>10472</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23918</t>
+          <t>24029</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47298</t>
+          <t>46833</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28213</t>
+          <t>28175</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>52106</t>
+          <t>53207</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2371990</t>
+          <t>2370679</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2478956</t>
+          <t>2478247</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2445055</t>
+          <t>2447029</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2558099</t>
+          <t>2555724</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4846843</t>
+          <t>4850722</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5003892</t>
+          <t>5001681</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,16%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>794817</t>
+          <t>791752</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>895730</t>
+          <t>894564</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>857941</t>
+          <t>857458</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>964596</t>
+          <t>961957</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1677540</t>
+          <t>1677980</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1838600</t>
+          <t>1827500</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>111565</t>
+          <t>112425</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>157834</t>
+          <t>158759</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>96744</t>
+          <t>97597</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>141847</t>
+          <t>141246</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>221480</t>
+          <t>223788</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>286039</t>
+          <t>288693</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>319422</t>
+          <t>319193</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>354429</t>
+          <t>354993</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>251398</t>
+          <t>250724</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>282570</t>
+          <t>283839</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>581481</t>
+          <t>581377</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>630083</t>
+          <t>630249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,75%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61136</t>
+          <t>60235</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94011</t>
+          <t>93305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52546</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80937</t>
+          <t>81268</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121220</t>
+          <t>120804</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165451</t>
+          <t>166093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22369</t>
+          <t>22374</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19236</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33902</t>
+          <t>34580</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>267071</t>
+          <t>269456</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>300655</t>
+          <t>301519</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262057</t>
+          <t>259597</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>296911</t>
+          <t>294816</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>540542</t>
+          <t>539162</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>586585</t>
+          <t>587541</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67403</t>
+          <t>66105</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100448</t>
+          <t>98348</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61725</t>
+          <t>62640</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94549</t>
+          <t>95093</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>138590</t>
+          <t>136623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>184619</t>
+          <t>183507</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19017</t>
+          <t>19767</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10245</t>
+          <t>10152</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27956</t>
+          <t>26853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>373181</t>
+          <t>372842</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>413413</t>
+          <t>411683</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>123817</t>
+          <t>123672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>143839</t>
+          <t>144047</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>504631</t>
+          <t>507190</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>549553</t>
+          <t>548264</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88023</t>
+          <t>87804</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122940</t>
+          <t>122849</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17620</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37050</t>
+          <t>37672</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112241</t>
+          <t>110933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151778</t>
+          <t>150344</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33157</t>
+          <t>34096</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12210</t>
+          <t>12156</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18700</t>
+          <t>18927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41465</t>
+          <t>40097</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>805115</t>
+          <t>802777</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>865266</t>
+          <t>865531</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>602389</t>
+          <t>602962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>653370</t>
+          <t>653574</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1424410</t>
+          <t>1423280</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1504448</t>
+          <t>1503514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,44%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>230257</t>
+          <t>230275</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>286525</t>
+          <t>291512</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142817</t>
+          <t>140983</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191604</t>
+          <t>189962</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386307</t>
+          <t>390362</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>464352</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37891</t>
+          <t>38980</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68913</t>
+          <t>67036</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18013</t>
+          <t>17936</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37913</t>
+          <t>38222</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>61520</t>
+          <t>61521</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>96582</t>
+          <t>97360</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>467696</t>
+          <t>468572</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>508053</t>
+          <t>507324</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>523997</t>
+          <t>524069</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>569905</t>
+          <t>572062</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1007791</t>
+          <t>1004700</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1066745</t>
+          <t>1068365</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,32%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91844</t>
+          <t>91568</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>129192</t>
+          <t>129703</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>131691</t>
+          <t>129862</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>175908</t>
+          <t>175808</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>233864</t>
+          <t>233216</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>293213</t>
+          <t>294388</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>26539</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>20705</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41481</t>
+          <t>42857</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34543</t>
+          <t>34106</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60644</t>
+          <t>62114</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>215574</t>
+          <t>213726</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>243414</t>
+          <t>241648</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>773356</t>
+          <t>774874</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>833801</t>
+          <t>833007</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1001926</t>
+          <t>1003721</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1067210</t>
+          <t>1067189</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34888</t>
+          <t>36344</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60141</t>
+          <t>62672</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>200420</t>
+          <t>201138</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>257039</t>
+          <t>257853</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>243939</t>
+          <t>246893</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>306477</t>
+          <t>306822</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24744</t>
+          <t>25644</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51918</t>
+          <t>52711</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30794</t>
+          <t>32372</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58489</t>
+          <t>60646</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2516162</t>
+          <t>2516051</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2614429</t>
+          <t>2616173</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2614285</t>
+          <t>2614418</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2722642</t>
+          <t>2718380</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5163471</t>
+          <t>5168662</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5302836</t>
+          <t>5311563</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>636161</t>
+          <t>639118</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>731182</t>
+          <t>734636</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>665112</t>
+          <t>668017</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>764995</t>
+          <t>768615</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1333433</t>
+          <t>1330828</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1461295</t>
+          <t>1464083</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97190</t>
+          <t>96747</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>142584</t>
+          <t>140352</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>99151</t>
+          <t>98995</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>145650</t>
+          <t>143301</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>206154</t>
+          <t>206628</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>272598</t>
+          <t>268041</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -7579,32 +7579,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>417588</t>
+          <t>454506</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>396820</t>
+          <t>431186</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>433509</t>
+          <t>474362</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7614,32 +7614,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>386502</t>
+          <t>419718</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>371566</t>
+          <t>403829</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>398975</t>
+          <t>432385</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7649,32 +7649,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>804091</t>
+          <t>874224</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>780107</t>
+          <t>848166</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>825656</t>
+          <t>899638</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,93%</t>
         </is>
       </c>
     </row>
@@ -7692,32 +7692,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64558</t>
+          <t>72656</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50118</t>
+          <t>57588</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81311</t>
+          <t>91569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7727,32 +7727,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47864</t>
+          <t>54423</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37563</t>
+          <t>42161</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62216</t>
+          <t>70512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7762,32 +7762,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>112423</t>
+          <t>127079</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94461</t>
+          <t>105668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132718</t>
+          <t>151317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21963</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>12334</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40723</t>
+          <t>38016</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7840,17 +7840,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10493</t>
+          <t>11478</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17594</t>
+          <t>18412</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>32456</t>
+          <t>33642</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21976</t>
+          <t>22213</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50622</t>
+          <t>50428</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -7918,17 +7918,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>504109</t>
+          <t>549327</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>504109</t>
+          <t>549327</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>504109</t>
+          <t>549327</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7953,17 +7953,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>444859</t>
+          <t>485619</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>444859</t>
+          <t>485619</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>444859</t>
+          <t>485619</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7988,17 +7988,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>948969</t>
+          <t>1034946</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>948969</t>
+          <t>1034946</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>948969</t>
+          <t>1034946</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8035,32 +8035,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>390112</t>
+          <t>416815</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>374736</t>
+          <t>399712</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404784</t>
+          <t>431001</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8070,32 +8070,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>312962</t>
+          <t>346103</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299454</t>
+          <t>331860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>325798</t>
+          <t>359877</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8105,17 +8105,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>703073</t>
+          <t>762917</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>683246</t>
+          <t>740666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>721589</t>
+          <t>785031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,8%</t>
         </is>
       </c>
     </row>
@@ -8148,32 +8148,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50567</t>
+          <t>53506</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38208</t>
+          <t>40322</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65486</t>
+          <t>69747</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8183,32 +8183,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>55646</t>
+          <t>61896</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44747</t>
+          <t>50194</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68644</t>
+          <t>74890</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8218,32 +8218,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>106213</t>
+          <t>115402</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>89624</t>
+          <t>94769</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>126439</t>
+          <t>134972</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19027</t>
+          <t>22101</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>8948</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21911</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>24189</t>
+          <t>26119</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15817</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34419</t>
+          <t>38247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -8374,17 +8374,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>451057</t>
+          <t>482031</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>451057</t>
+          <t>482031</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>451057</t>
+          <t>482031</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8409,17 +8409,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382419</t>
+          <t>422407</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382419</t>
+          <t>422407</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382419</t>
+          <t>422407</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8444,17 +8444,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>833475</t>
+          <t>904438</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>833475</t>
+          <t>904438</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>833475</t>
+          <t>904438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8491,32 +8491,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>590058</t>
+          <t>387223</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536686</t>
+          <t>370696</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>638629</t>
+          <t>404222</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8526,32 +8526,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>140125</t>
+          <t>156988</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>131568</t>
+          <t>146636</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>147091</t>
+          <t>164803</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8561,32 +8561,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>730183</t>
+          <t>544210</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>679806</t>
+          <t>522794</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>783959</t>
+          <t>562675</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>85,45%</t>
         </is>
       </c>
     </row>
@@ -8604,32 +8604,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57129</t>
+          <t>62189</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21276</t>
+          <t>47400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98528</t>
+          <t>77713</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8639,32 +8639,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21998</t>
+          <t>24647</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>17693</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30342</t>
+          <t>33797</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8674,32 +8674,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>79127</t>
+          <t>86836</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35709</t>
+          <t>71280</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117866</t>
+          <t>105591</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -8717,32 +8717,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21077</t>
+          <t>22201</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>13753</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>33770</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8752,32 +8752,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>10874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8787,32 +8787,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>25275</t>
+          <t>27409</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41251</t>
+          <t>40100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -8830,17 +8830,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8865,17 +8865,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166321</t>
+          <t>186843</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166321</t>
+          <t>186843</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166321</t>
+          <t>186843</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8900,17 +8900,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>834585</t>
+          <t>658455</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>834585</t>
+          <t>658455</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>834585</t>
+          <t>658455</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8947,32 +8947,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>857407</t>
+          <t>938706</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>826494</t>
+          <t>911380</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>883584</t>
+          <t>965192</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8982,32 +8982,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>840197</t>
+          <t>701716</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>797368</t>
+          <t>680877</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>915609</t>
+          <t>720356</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9017,32 +9017,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1697605</t>
+          <t>1640422</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1649094</t>
+          <t>1601728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1805450</t>
+          <t>1673879</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>84,32%</t>
         </is>
       </c>
     </row>
@@ -9060,32 +9060,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>127486</t>
+          <t>135033</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105313</t>
+          <t>111885</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156793</t>
+          <t>162451</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9095,32 +9095,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>106674</t>
+          <t>121695</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47787</t>
+          <t>105431</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142583</t>
+          <t>141820</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9130,32 +9130,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>234160</t>
+          <t>256727</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>156821</t>
+          <t>227791</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>279361</t>
+          <t>287906</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -9173,67 +9173,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45488</t>
+          <t>52303</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32180</t>
+          <t>37706</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63479</t>
+          <t>70571</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>35684</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>26824</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>47761</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
           <t>3,12%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>29212</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>13189</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>41846</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9243,32 +9243,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74700</t>
+          <t>87987</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50964</t>
+          <t>71652</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>95852</t>
+          <t>111418</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -9286,17 +9286,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1030381</t>
+          <t>1126041</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1030381</t>
+          <t>1126041</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1030381</t>
+          <t>1126041</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9321,17 +9321,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>976083</t>
+          <t>859095</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>976083</t>
+          <t>859095</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>976083</t>
+          <t>859095</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9356,17 +9356,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2006465</t>
+          <t>1985136</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2006465</t>
+          <t>1985136</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2006465</t>
+          <t>1985136</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9403,32 +9403,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>389186</t>
+          <t>466064</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>369247</t>
+          <t>446438</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>403632</t>
+          <t>483934</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9438,32 +9438,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>689897</t>
+          <t>653631</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>663588</t>
+          <t>631799</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>728878</t>
+          <t>673520</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9473,32 +9473,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1079083</t>
+          <t>1119695</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1048167</t>
+          <t>1090905</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1121290</t>
+          <t>1146608</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -9516,32 +9516,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>57130</t>
+          <t>69950</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44753</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>73401</t>
+          <t>87356</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9551,32 +9551,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>101093</t>
+          <t>114163</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>73115</t>
+          <t>97094</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>121102</t>
+          <t>130420</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9586,32 +9586,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>158223</t>
+          <t>184113</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>128400</t>
+          <t>161807</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>182385</t>
+          <t>206897</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -9629,32 +9629,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>26292</t>
+          <t>29690</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>20984</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37144</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9664,32 +9664,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>48897</t>
+          <t>60437</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35258</t>
+          <t>48223</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64674</t>
+          <t>76220</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>5,82%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9699,32 +9699,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>75189</t>
+          <t>90127</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56825</t>
+          <t>73207</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93479</t>
+          <t>108897</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -9742,17 +9742,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>472608</t>
+          <t>565705</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>472608</t>
+          <t>565705</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>472608</t>
+          <t>565705</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9777,17 +9777,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>839887</t>
+          <t>828231</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>839887</t>
+          <t>828231</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>839887</t>
+          <t>828231</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9812,17 +9812,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1312495</t>
+          <t>1393935</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1312495</t>
+          <t>1393935</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1312495</t>
+          <t>1393935</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9844,7 +9844,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9859,32 +9859,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>194819</t>
+          <t>188978</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>171115</t>
+          <t>167482</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>211924</t>
+          <t>207382</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9894,32 +9894,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>624583</t>
+          <t>694545</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>601317</t>
+          <t>672069</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>644908</t>
+          <t>714654</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9929,32 +9929,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>819403</t>
+          <t>883523</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>788194</t>
+          <t>850516</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>844717</t>
+          <t>909146</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -9972,32 +9972,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>29696</t>
+          <t>31635</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15122</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47077</t>
+          <t>50807</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10007,32 +10007,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>103962</t>
+          <t>111997</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87115</t>
+          <t>94407</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>124616</t>
+          <t>134743</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10042,32 +10042,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>133658</t>
+          <t>143632</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>111229</t>
+          <t>121721</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>164091</t>
+          <t>170083</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -10085,32 +10085,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>14915</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33694</t>
+          <t>31813</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10120,32 +10120,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>30656</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21185</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45670</t>
+          <t>50155</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10155,32 +10155,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>45571</t>
+          <t>50923</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31094</t>
+          <t>36583</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>65311</t>
+          <t>71030</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -10198,17 +10198,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10233,17 +10233,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>759201</t>
+          <t>841948</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>759201</t>
+          <t>841948</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>759201</t>
+          <t>841948</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10268,17 +10268,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>998632</t>
+          <t>1078078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>998632</t>
+          <t>1078078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>998632</t>
+          <t>1078078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10315,32 +10315,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2839171</t>
+          <t>2852290</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2780108</t>
+          <t>2803828</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2978687</t>
+          <t>2906322</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10350,32 +10350,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2994267</t>
+          <t>2972701</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2936888</t>
+          <t>2929272</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3102764</t>
+          <t>3014606</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10385,32 +10385,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5833438</t>
+          <t>5824991</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5731257</t>
+          <t>5756624</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5977863</t>
+          <t>5885013</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -10428,32 +10428,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>386567</t>
+          <t>424970</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>285221</t>
+          <t>379256</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>435147</t>
+          <t>466914</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10463,32 +10463,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>437237</t>
+          <t>488821</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>361158</t>
+          <t>453137</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>486188</t>
+          <t>526038</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10498,32 +10498,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>823804</t>
+          <t>913790</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>720807</t>
+          <t>859884</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>911476</t>
+          <t>977922</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -10541,32 +10541,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>140113</t>
+          <t>153585</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>106968</t>
+          <t>126396</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>169549</t>
+          <t>183661</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10576,32 +10576,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>137266</t>
+          <t>162621</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109929</t>
+          <t>142668</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>162461</t>
+          <t>188842</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10611,32 +10611,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>277379</t>
+          <t>316207</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>234352</t>
+          <t>279513</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>320129</t>
+          <t>349944</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -10654,17 +10654,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3365851</t>
+          <t>3430845</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3365851</t>
+          <t>3430845</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3365851</t>
+          <t>3430845</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10689,17 +10689,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3568770</t>
+          <t>3624143</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3568770</t>
+          <t>3624143</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3568770</t>
+          <t>3624143</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10724,17 +10724,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6934621</t>
+          <t>7054988</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6934621</t>
+          <t>7054988</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6934621</t>
+          <t>7054988</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
